--- a/data/trans_dic/P6902-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,11; 54,11</t>
+          <t>24,91; 53,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,79; 91,59</t>
+          <t>33,29; 91,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 60,49</t>
+          <t>12,97; 59,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 96,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,16; 70,43</t>
+          <t>27,77; 70,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,64; 89,38</t>
+          <t>28,21; 89,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,93; 91,37</t>
+          <t>32,71; 91,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,04; 100,0</t>
+          <t>54,0; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,83; 54,52</t>
+          <t>30,23; 53,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,15; 83,21</t>
+          <t>38,84; 83,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29,06; 65,53</t>
+          <t>30,11; 67,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,25; 94,16</t>
+          <t>42,62; 95,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,87; 52,82</t>
+          <t>35,1; 52,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,46; 64,33</t>
+          <t>42,55; 64,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,9; 47,01</t>
+          <t>26,5; 47,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,62; 87,14</t>
+          <t>58,98; 88,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,56; 68,19</t>
+          <t>46,35; 67,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,56; 66,25</t>
+          <t>41,47; 66,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,24; 73,99</t>
+          <t>45,28; 72,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,16; 82,21</t>
+          <t>55,06; 81,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,89; 55,21</t>
+          <t>41,03; 54,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,66; 62,91</t>
+          <t>45,43; 62,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,89; 53,52</t>
+          <t>35,9; 53,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,68; 81,25</t>
+          <t>62,25; 82,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,31; 54,6</t>
+          <t>37,98; 55,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,02; 58,06</t>
+          <t>37,69; 57,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,43; 48,28</t>
+          <t>29,42; 49,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,52; 64,64</t>
+          <t>43,09; 65,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,78; 62,39</t>
+          <t>38,59; 62,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,9; 72,03</t>
+          <t>49,07; 72,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,18; 72,62</t>
+          <t>51,04; 73,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50,65; 69,12</t>
+          <t>51,55; 69,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,88; 54,77</t>
+          <t>40,37; 54,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,32; 61,63</t>
+          <t>44,88; 60,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,7; 55,2</t>
+          <t>40,22; 54,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,53; 64,58</t>
+          <t>49,72; 63,91</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,83; 55,99</t>
+          <t>37,06; 56,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,22; 49,16</t>
+          <t>28,18; 48,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,23; 61,91</t>
+          <t>39,72; 61,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,95; 70,58</t>
+          <t>52,69; 71,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,49; 65,78</t>
+          <t>33,64; 65,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,14; 66,07</t>
+          <t>35,35; 67,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,56; 70,49</t>
+          <t>41,51; 69,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 69,12</t>
+          <t>25,46; 70,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,54; 55,89</t>
+          <t>38,62; 56,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,86; 51,33</t>
+          <t>33,86; 52,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44,26; 61,13</t>
+          <t>43,9; 61,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,5; 67,51</t>
+          <t>35,93; 67,18</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,88; 46,67</t>
+          <t>18,19; 45,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,36; 60,17</t>
+          <t>32,33; 60,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,1; 69,98</t>
+          <t>39,57; 71,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,2; 74,1</t>
+          <t>50,95; 74,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,2; 62,15</t>
+          <t>14,38; 64,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,98; 82,73</t>
+          <t>41,33; 82,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,47; 81,15</t>
+          <t>42,96; 81,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>57,72; 75,2</t>
+          <t>56,98; 75,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,58; 43,61</t>
+          <t>21,4; 44,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,61; 64,84</t>
+          <t>40,65; 65,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,97; 69,81</t>
+          <t>45,44; 70,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,64; 71,88</t>
+          <t>57,38; 71,63</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 86,98</t>
+          <t>0,0; 82,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,19; 100,0</t>
+          <t>12,37; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,97; 77,33</t>
+          <t>15,1; 77,67</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,71; 48,01</t>
+          <t>39,26; 48,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,96; 52,55</t>
+          <t>41,42; 52,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,8; 48,77</t>
+          <t>37,98; 49,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,4; 67,04</t>
+          <t>56,08; 67,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,02; 58,75</t>
+          <t>44,37; 57,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50,04; 64,04</t>
+          <t>49,92; 64,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,61; 67,05</t>
+          <t>53,8; 66,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,3; 68,86</t>
+          <t>42,76; 68,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,18; 49,68</t>
+          <t>42,3; 49,9</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46,69; 55,53</t>
+          <t>46,55; 55,41</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45,38; 54,22</t>
+          <t>45,73; 54,37</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>51,16; 66,32</t>
+          <t>50,36; 65,77</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado</t>
+          <t>Población que su trabajo le afecta de manera que se siente nervioso y estresado (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11595; 24986</t>
+          <t>11499; 24507</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3283; 9459</t>
+          <t>3437; 9472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2163; 10374</t>
+          <t>2225; 10197</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5989</t>
+          <t>0; 5795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5592; 13988</t>
+          <t>5515; 13999</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2880; 8989</t>
+          <t>2837; 8986</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3717; 10638</t>
+          <t>3809; 10656</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8292; 15344</t>
+          <t>8286; 15344</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20358; 35999</t>
+          <t>19963; 35254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7776; 16961</t>
+          <t>7917; 17038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8368; 18869</t>
+          <t>8669; 19382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8373; 20087</t>
+          <t>9092; 20285</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51034; 75156</t>
+          <t>49950; 74930</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35773; 55511</t>
+          <t>36711; 56027</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21128; 38348</t>
+          <t>21619; 38764</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33447; 51480</t>
+          <t>34840; 52485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35326; 54060</t>
+          <t>36747; 53431</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27890; 44464</t>
+          <t>27834; 44728</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21407; 34251</t>
+          <t>20962; 33686</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28052; 41063</t>
+          <t>27504; 40790</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92821; 122321</t>
+          <t>90904; 121623</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70045; 96511</t>
+          <t>69697; 95551</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47166; 68432</t>
+          <t>45901; 68866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66154; 88575</t>
+          <t>67865; 89609</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45760; 68817</t>
+          <t>47861; 70299</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37208; 56829</t>
+          <t>36894; 56008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33293; 54616</t>
+          <t>33279; 55784</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41573; 61749</t>
+          <t>41163; 62219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27165; 43701</t>
+          <t>27031; 43470</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36241; 52320</t>
+          <t>35637; 52937</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35854; 51895</t>
+          <t>36475; 52446</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38267; 52225</t>
+          <t>38948; 52540</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80159; 107394</t>
+          <t>79154; 107099</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77270; 105088</t>
+          <t>76519; 103621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75123; 101895</t>
+          <t>74247; 101408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84746; 110482</t>
+          <t>85067; 109347</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40925; 62215</t>
+          <t>41177; 62767</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25056; 43642</t>
+          <t>25016; 43004</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36785; 56607</t>
+          <t>36312; 55802</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56394; 76617</t>
+          <t>57196; 77371</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12034; 24361</t>
+          <t>12460; 24277</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13735; 27383</t>
+          <t>14652; 27887</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23880; 39550</t>
+          <t>23291; 39097</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40377; 107101</t>
+          <t>39447; 109072</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57090; 82797</t>
+          <t>57212; 83033</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44099; 66843</t>
+          <t>44094; 67911</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65303; 90194</t>
+          <t>64764; 90228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>101449; 177887</t>
+          <t>94669; 177022</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8664; 21411</t>
+          <t>8348; 20711</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13121; 25170</t>
+          <t>13527; 25253</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17537; 31387</t>
+          <t>17746; 31872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33854; 49969</t>
+          <t>34359; 50357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1975; 8644</t>
+          <t>2000; 9001</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9828; 20337</t>
+          <t>10159; 20347</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13081; 24994</t>
+          <t>13231; 24951</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32041; 41741</t>
+          <t>31628; 41739</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11704; 26072</t>
+          <t>12795; 26676</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26310; 43063</t>
+          <t>26995; 43245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35530; 52810</t>
+          <t>34371; 53460</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>69639; 88372</t>
+          <t>70544; 88059</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>810; 1880</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2542</t>
+          <t>0; 2401</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>559; 2914</t>
+          <t>361; 2914</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>810; 1880</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1049; 4513</t>
+          <t>881; 4533</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>182842; 226766</t>
+          <t>185412; 229307</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>133156; 170842</t>
+          <t>134651; 170371</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>132290; 170699</t>
+          <t>132941; 171739</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>191466; 227618</t>
+          <t>190398; 227815</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>99095; 129325</t>
+          <t>97668; 126680</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>108010; 138217</t>
+          <t>107731; 138490</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>115947; 145027</t>
+          <t>116377; 144767</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>149821; 243927</t>
+          <t>151457; 241655</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>292085; 343979</t>
+          <t>292908; 345489</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>252559; 300396</t>
+          <t>251828; 299706</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>256966; 307060</t>
+          <t>258995; 307871</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>354902; 460070</t>
+          <t>349388; 456275</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6902-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6902-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,91; 53,08</t>
+          <t>26,41; 55,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,29; 91,72</t>
+          <t>31,45; 91,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,97; 59,45</t>
+          <t>12,73; 62,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 96,75</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,77; 70,49</t>
+          <t>27,49; 70,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,21; 89,36</t>
+          <t>27,62; 88,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,71; 91,52</t>
+          <t>32,84; 91,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,0; 100,0</t>
+          <t>52,38; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,23; 53,39</t>
+          <t>29,57; 54,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38,84; 83,59</t>
+          <t>37,94; 81,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,11; 67,31</t>
+          <t>28,26; 65,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,62; 95,09</t>
+          <t>37,51; 90,96</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,1; 52,66</t>
+          <t>34,5; 53,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,55; 64,93</t>
+          <t>42,09; 64,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,5; 47,52</t>
+          <t>26,09; 47,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58,98; 88,85</t>
+          <t>62,49; 87,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,35; 67,4</t>
+          <t>45,48; 67,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,47; 66,65</t>
+          <t>41,89; 67,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,28; 72,77</t>
+          <t>44,0; 73,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>55,06; 81,66</t>
+          <t>55,7; 81,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41,03; 54,89</t>
+          <t>41,48; 55,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,43; 62,29</t>
+          <t>45,38; 62,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,9; 53,86</t>
+          <t>35,89; 53,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,25; 82,19</t>
+          <t>62,05; 81,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,98; 55,78</t>
+          <t>36,59; 55,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,69; 57,22</t>
+          <t>37,57; 57,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,42; 49,31</t>
+          <t>29,02; 48,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,09; 65,13</t>
+          <t>44,05; 63,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,59; 62,06</t>
+          <t>38,1; 61,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,07; 72,89</t>
+          <t>49,88; 72,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,04; 73,39</t>
+          <t>51,65; 72,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,55; 69,54</t>
+          <t>51,85; 69,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,37; 54,62</t>
+          <t>40,5; 54,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44,88; 60,77</t>
+          <t>45,69; 61,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,22; 54,94</t>
+          <t>40,29; 54,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,72; 63,91</t>
+          <t>49,96; 62,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,06; 56,49</t>
+          <t>37,01; 56,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,18; 48,44</t>
+          <t>28,44; 49,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,72; 61,03</t>
+          <t>39,1; 61,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,69; 71,27</t>
+          <t>52,59; 71,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,64; 65,55</t>
+          <t>34,24; 66,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,35; 67,29</t>
+          <t>36,05; 68,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,51; 69,68</t>
+          <t>42,38; 68,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,46; 70,39</t>
+          <t>63,55; 76,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,62; 56,05</t>
+          <t>39,19; 56,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,86; 52,15</t>
+          <t>33,79; 52,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,9; 61,16</t>
+          <t>43,2; 61,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,93; 67,18</t>
+          <t>60,4; 71,8</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 45,14</t>
+          <t>17,83; 45,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,33; 60,37</t>
+          <t>31,22; 60,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,57; 71,07</t>
+          <t>39,09; 68,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,95; 74,67</t>
+          <t>51,54; 73,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,38; 64,71</t>
+          <t>14,43; 64,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,33; 82,77</t>
+          <t>41,37; 82,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,96; 81,01</t>
+          <t>42,42; 82,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,98; 75,2</t>
+          <t>55,68; 74,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 44,61</t>
+          <t>20,68; 44,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,65; 65,11</t>
+          <t>39,31; 64,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45,44; 70,67</t>
+          <t>45,67; 69,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,38; 71,63</t>
+          <t>56,99; 71,73</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,13</t>
+          <t>0,0; 82,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,37; 100,0</t>
+          <t>26,42; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,1; 77,67</t>
+          <t>16,31; 72,72</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>39,26; 48,55</t>
+          <t>38,46; 48,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41,42; 52,4</t>
+          <t>41,03; 52,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37,98; 49,07</t>
+          <t>38,13; 49,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,08; 67,1</t>
+          <t>55,96; 66,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,37; 57,55</t>
+          <t>44,12; 57,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,92; 64,17</t>
+          <t>49,47; 63,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,8; 66,93</t>
+          <t>53,42; 66,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,76; 68,22</t>
+          <t>62,92; 71,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,3; 49,9</t>
+          <t>41,73; 49,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46,55; 55,41</t>
+          <t>47,09; 55,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45,73; 54,37</t>
+          <t>45,54; 54,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,36; 65,77</t>
+          <t>60,51; 67,9</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16862</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11499; 24507</t>
+          <t>12192; 25448</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3437; 9472</t>
+          <t>3248; 9399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2225; 10197</t>
+          <t>2184; 10776</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5795</t>
+          <t>0; 9218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5515; 13999</t>
+          <t>5459; 14084</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2837; 8986</t>
+          <t>2778; 8891</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3809; 10656</t>
+          <t>3824; 10646</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8286; 15344</t>
+          <t>8327; 15899</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19963; 35254</t>
+          <t>19523; 35759</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7917; 17038</t>
+          <t>7732; 16521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8669; 19382</t>
+          <t>8137; 18884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9092; 20285</t>
+          <t>9422; 22846</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43875</t>
+          <t>53137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>35572</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79269</t>
+          <t>88709</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49950; 74930</t>
+          <t>49090; 75819</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36711; 56027</t>
+          <t>36319; 55451</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21619; 38764</t>
+          <t>21280; 38575</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34840; 52485</t>
+          <t>43487; 60744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36747; 53431</t>
+          <t>36056; 53631</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27834; 44728</t>
+          <t>28111; 45284</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20962; 33686</t>
+          <t>20367; 33883</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27504; 40790</t>
+          <t>28690; 42021</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90904; 121623</t>
+          <t>91895; 122390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69697; 95551</t>
+          <t>69620; 95197</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45901; 68866</t>
+          <t>45886; 68769</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67865; 89609</t>
+          <t>75144; 99125</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51614</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>52383</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>111688</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47861; 70299</t>
+          <t>46115; 69603</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36894; 56008</t>
+          <t>36775; 56220</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33279; 55784</t>
+          <t>32826; 54805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41163; 62219</t>
+          <t>48446; 69589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27031; 43470</t>
+          <t>26689; 42877</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35637; 52937</t>
+          <t>36229; 52975</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36475; 52446</t>
+          <t>36911; 51946</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38948; 52540</t>
+          <t>44920; 60032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79154; 107099</t>
+          <t>79406; 107314</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76519; 103621</t>
+          <t>77911; 104529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74247; 101408</t>
+          <t>74367; 101232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85067; 109347</t>
+          <t>98228; 123819</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67977</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>81449</t>
+          <t>88743</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>149426</t>
+          <t>163591</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41177; 62767</t>
+          <t>41125; 62799</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25016; 43004</t>
+          <t>25251; 44133</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36312; 55802</t>
+          <t>35751; 56286</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57196; 77371</t>
+          <t>63392; 86024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12460; 24277</t>
+          <t>12680; 24730</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14652; 27887</t>
+          <t>14942; 28258</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23291; 39097</t>
+          <t>23780; 38551</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39447; 109072</t>
+          <t>80403; 96658</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57212; 83033</t>
+          <t>58060; 84056</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44094; 67911</t>
+          <t>44006; 67856</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64764; 90228</t>
+          <t>63730; 90711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94669; 177022</t>
+          <t>149221; 177370</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>45851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>40400</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79633</t>
+          <t>86251</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8348; 20711</t>
+          <t>8178; 20802</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13527; 25253</t>
+          <t>13060; 25455</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17746; 31872</t>
+          <t>17529; 30858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34359; 50357</t>
+          <t>37118; 53082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2000; 9001</t>
+          <t>2007; 8993</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10159; 20347</t>
+          <t>10171; 20284</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13231; 24951</t>
+          <t>13064; 25345</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31628; 41739</t>
+          <t>34389; 45715</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12795; 26676</t>
+          <t>12367; 26780</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26995; 43245</t>
+          <t>26108; 42766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34371; 53460</t>
+          <t>34545; 52570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70544; 88059</t>
+          <t>76246; 95965</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2846</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2401</t>
+          <t>0; 3040</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>361; 2914</t>
+          <t>792; 2999</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>881; 4533</t>
+          <t>1088; 4848</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209966</t>
+          <t>237215</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>214322</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>424288</t>
+          <t>469947</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>185412; 229307</t>
+          <t>181641; 228714</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134651; 170371</t>
+          <t>133393; 169246</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>132941; 171739</t>
+          <t>133469; 171833</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>190398; 227815</t>
+          <t>215437; 255905</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97668; 126680</t>
+          <t>97113; 126572</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>107731; 138490</t>
+          <t>106769; 137870</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>116377; 144767</t>
+          <t>115538; 144165</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>151457; 241655</t>
+          <t>217276; 247807</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>292908; 345489</t>
+          <t>288922; 342872</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>251828; 299706</t>
+          <t>254735; 302557</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>258995; 307871</t>
+          <t>257887; 306843</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>349388; 456275</t>
+          <t>441934; 495872</t>
         </is>
       </c>
     </row>
